--- a/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Bavaria insights/[Bavaria][Manhattan][CI]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -481,13 +493,13 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9773684740066528</v>
+        <v>0.9684882164001465</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7362380623817444</v>
+        <v>0.4784467816352844</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.9083609580993652</v>
+        <v>0.9726020693778992</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05931780114769936</v>
+        <v>0.8449468016624451</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -519,24 +531,24 @@
         <v>31</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9392668008804321</v>
+        <v>0.9237709641456604</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07875461876392365</v>
+        <v>0.02975904569029808</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9266648292541504</v>
+        <v>0.943225085735321</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1331817656755447</v>
+        <v>0.3287301957607269</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -557,13 +569,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9800883531570435</v>
+        <v>0.9823178648948669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.81516033411026</v>
+        <v>0.8735049366950989</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.9295345544815063</v>
+        <v>0.9131664037704468</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1512637883424759</v>
+        <v>0.09784942120313644</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -595,13 +607,13 @@
         <v>31</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9560911655426025</v>
+        <v>0.9641954302787781</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2292193472385406</v>
+        <v>0.3749898374080658</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8927256464958191</v>
+        <v>0.8727952837944031</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03019031137228012</v>
+        <v>0.01978909038007259</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -633,13 +645,13 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9467556476593018</v>
+        <v>0.9496957659721375</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1269688904285431</v>
+        <v>0.1531190127134323</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,10 +659,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.9068124294281006</v>
+        <v>0.918255090713501</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05543487891554832</v>
+        <v>0.1203928142786026</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -671,13 +683,13 @@
         <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9393754601478577</v>
+        <v>0.9369224309921265</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07930121570825577</v>
+        <v>0.06785309314727783</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.9254050254821777</v>
+        <v>0.9153565764427185</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1259382963180542</v>
+        <v>0.1069763749837875</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -709,13 +721,13 @@
         <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9710994958877563</v>
+        <v>0.9742333292961121</v>
       </c>
       <c r="F8" t="n">
-        <v>0.549806535243988</v>
+        <v>0.6416910290718079</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9706977605819702</v>
+        <v>0.9605152010917664</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7695406079292297</v>
+        <v>0.6116103529930115</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -747,13 +759,13 @@
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8831111192703247</v>
+        <v>0.8966581225395203</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002802361501380801</v>
+        <v>0.005954447668045759</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.9574397206306458</v>
+        <v>0.9435487985610962</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4940563440322876</v>
+        <v>0.3328783810138702</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -785,13 +797,13 @@
         <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9630038738250732</v>
+        <v>0.9688726663589478</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3495646417140961</v>
+        <v>0.4885842502117157</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.9410768747329712</v>
+        <v>0.9378263354301453</v>
       </c>
       <c r="I10" t="n">
-        <v>0.251266211271286</v>
+        <v>0.2659059762954712</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -823,13 +835,13 @@
         <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9457932114601135</v>
+        <v>0.9431688785552979</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1194076687097549</v>
+        <v>0.1009937450289726</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.879732608795166</v>
+        <v>0.8929632306098938</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01749767176806927</v>
+        <v>0.04339345172047615</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -861,13 +873,13 @@
         <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9532337188720703</v>
+        <v>0.9412752985954285</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1915912628173828</v>
+        <v>0.08950322866439819</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9857861995697021</v>
+        <v>0.9823969006538391</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9859299063682556</v>
+        <v>0.9713158011436462</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -899,13 +911,13 @@
         <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9358055591583252</v>
+        <v>0.9380552768707275</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06321439892053604</v>
+        <v>0.07291454076766968</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.953981339931488</v>
+        <v>0.960158109664917</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4315818548202515</v>
+        <v>0.6046861410140991</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -937,13 +949,13 @@
         <v>31</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>0.950918972492218</v>
+        <v>0.9469496011734009</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1654894798994064</v>
+        <v>0.1285490542650223</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8641678094863892</v>
+        <v>0.8625036478042603</v>
       </c>
       <c r="I14" t="n">
-        <v>0.009294215589761734</v>
+        <v>0.01341959834098816</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -975,13 +987,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8980455994606018</v>
+        <v>0.8948104381561279</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00644442206248641</v>
+        <v>0.005362259224057198</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9369370937347412</v>
+        <v>0.90770423412323</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2097331285476685</v>
+        <v>0.07838614284992218</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1013,13 +1025,13 @@
         <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>0.967745840549469</v>
+        <v>0.9737594127655029</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4592604041099548</v>
+        <v>0.6274933815002441</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9371346831321716</v>
+        <v>0.9482665657997131</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2115589082241058</v>
+        <v>0.3984759151935577</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1051,13 +1063,13 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9594752192497253</v>
+        <v>0.9641242027282715</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2825618088245392</v>
+        <v>0.3734303414821625</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.9677227735519409</v>
+        <v>0.9853563904762268</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7062482237815857</v>
+        <v>0.9883637428283691</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1089,13 +1101,13 @@
         <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9171753525733948</v>
+        <v>0.9042606949806213</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0198777262121439</v>
+        <v>0.009223811328411102</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9428656101226807</v>
+        <v>0.9494562149047852</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2714669108390808</v>
+        <v>0.4165505468845367</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1127,24 +1139,24 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9283470511436462</v>
+        <v>0.9343437552452087</v>
       </c>
       <c r="F19" t="n">
-        <v>0.03953760489821434</v>
+        <v>0.05762941390275955</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8629555702209473</v>
+        <v>0.839482307434082</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008855885826051235</v>
+        <v>0.005806175991892815</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1165,13 +1177,13 @@
         <v>31</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9282685518264771</v>
+        <v>0.9159140586853027</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03934435173869133</v>
+        <v>0.01841719262301922</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9264456629753113</v>
+        <v>0.9229419231414795</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1318923979997635</v>
+        <v>0.1457486003637314</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1203,13 +1215,13 @@
         <v>31</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9695704579353333</v>
+        <v>0.9504496455192566</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5073233246803284</v>
+        <v>0.1606326103210449</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,14 +1229,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.9067339301109314</v>
+        <v>0.8754552602767944</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05524512007832527</v>
+        <v>0.02190917544066906</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1241,13 +1253,13 @@
         <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9428743124008179</v>
+        <v>0.9458401799201965</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09911330044269562</v>
+        <v>0.1197657138109207</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8821849822998047</v>
+        <v>0.8758313655853271</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01937209069728851</v>
+        <v>0.02222773432731628</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1279,13 +1291,13 @@
         <v>31</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9794087409973145</v>
+        <v>0.9787393808364868</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7960332036018372</v>
+        <v>0.7767488360404968</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9449130892753601</v>
+        <v>0.9361805319786072</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2963822484016418</v>
+        <v>0.2490321546792984</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1317,13 +1329,13 @@
         <v>31</v>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.974112868309021</v>
+        <v>0.9585757255554199</v>
       </c>
       <c r="F24" t="n">
-        <v>0.63807612657547</v>
+        <v>0.2673874795436859</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.9542860984802246</v>
+        <v>0.9397144913673401</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4368509948253632</v>
+        <v>0.2865424454212189</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1355,13 +1367,13 @@
         <v>31</v>
       </c>
       <c r="D25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9707260727882385</v>
+        <v>0.9735943078994751</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5392609834671021</v>
+        <v>0.6225662231445312</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.9409201145172119</v>
+        <v>0.9394144415855408</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2495636194944382</v>
+        <v>0.2831697762012482</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1393,13 +1405,13 @@
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8770578503608704</v>
+        <v>0.845049262046814</v>
       </c>
       <c r="F26" t="n">
-        <v>0.00202228338457644</v>
+        <v>0.0003981275367550552</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,10 +1419,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.9150535464286804</v>
+        <v>0.9277164340019226</v>
       </c>
       <c r="I26" t="n">
-        <v>0.07961136102676392</v>
+        <v>0.1770114749670029</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1431,13 +1443,13 @@
         <v>31</v>
       </c>
       <c r="D27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9609987139701843</v>
+        <v>0.9751836061477661</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3099982440471649</v>
+        <v>0.6703346371650696</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8737302422523499</v>
+        <v>0.8670283555984497</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01367224380373955</v>
+        <v>0.01590175367891788</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1469,13 +1481,13 @@
         <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9541484713554382</v>
+        <v>0.95326167345047</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2029528319835663</v>
+        <v>0.1919291019439697</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.907197892665863</v>
+        <v>0.904441237449646</v>
       </c>
       <c r="I28" t="n">
-        <v>0.05637616291642189</v>
+        <v>0.0686987116932869</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1507,13 +1519,13 @@
         <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9758374691009521</v>
+        <v>0.9785304069519043</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6901101469993591</v>
+        <v>0.7706503868103027</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9531222581863403</v>
+        <v>0.9527480006217957</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4169811904430389</v>
+        <v>0.4697375893592834</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1545,13 +1557,13 @@
         <v>31</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9088906645774841</v>
+        <v>0.912447452545166</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01210416108369827</v>
+        <v>0.01495420839637518</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.9274371862411499</v>
+        <v>0.9314588308334351</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1378260105848312</v>
+        <v>0.2059924155473709</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1583,13 +1595,13 @@
         <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9720900058746338</v>
+        <v>0.9769625663757324</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5782546997070312</v>
+        <v>0.724064826965332</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.9313843250274658</v>
+        <v>0.9168572425842285</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1641810238361359</v>
+        <v>0.1137228384613991</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1621,13 +1633,13 @@
         <v>31</v>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9255517721176147</v>
+        <v>0.9299917817115784</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03322546556591988</v>
+        <v>0.04382143914699554</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.9580585956573486</v>
+        <v>0.965051531791687</v>
       </c>
       <c r="I32" t="n">
-        <v>0.505832850933075</v>
+        <v>0.7011792063713074</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1659,13 +1671,13 @@
         <v>31</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9518039226531982</v>
+        <v>0.9507813453674316</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1750370711088181</v>
+        <v>0.1640512049198151</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,14 +1685,14 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9241008758544922</v>
+        <v>0.8834363222122192</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1188545972108841</v>
+        <v>0.02983232773840427</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -1697,13 +1709,13 @@
         <v>31</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9620973467826843</v>
+        <v>0.9581900835037231</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3311815857887268</v>
+        <v>0.2611075341701508</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9379902482032776</v>
+        <v>0.9480665326118469</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2196404486894608</v>
+        <v>0.3954982161521912</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1735,13 +1747,13 @@
         <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9553699493408203</v>
+        <v>0.961301326751709</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2191182374954224</v>
+        <v>0.3157148957252502</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9380809664726257</v>
+        <v>0.9332539439201355</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2205141484737396</v>
+        <v>0.2214563339948654</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1773,13 +1785,13 @@
         <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9698234796524048</v>
+        <v>0.9690058827400208</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5142223834991455</v>
+        <v>0.492127925157547</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9642207026481628</v>
+        <v>0.954491138458252</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6311364769935608</v>
+        <v>0.4997231960296631</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1811,13 +1823,13 @@
         <v>31</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9746038913726807</v>
+        <v>0.9754965305328369</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6528391242027283</v>
+        <v>0.6797981858253479</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,14 +1837,14 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.8907031416893005</v>
+        <v>0.9197269678115845</v>
       </c>
       <c r="I37" t="n">
-        <v>0.02770504914224148</v>
+        <v>0.1278406530618668</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1849,13 +1861,13 @@
         <v>31</v>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9634193778038025</v>
+        <v>0.966609001159668</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3582676649093628</v>
+        <v>0.4309057593345642</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.9540769457817078</v>
+        <v>0.9517303109169006</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4332295060157776</v>
+        <v>0.4528038501739502</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1887,13 +1899,13 @@
         <v>31</v>
       </c>
       <c r="D39" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9842146039009094</v>
+        <v>0.9859194159507751</v>
       </c>
       <c r="F39" t="n">
-        <v>0.915931761264801</v>
+        <v>0.9468458294868469</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,14 +1913,14 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.9006052017211914</v>
+        <v>0.9230166673660278</v>
       </c>
       <c r="I39" t="n">
-        <v>0.04233091324567795</v>
+        <v>0.1461931765079498</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1925,13 +1937,13 @@
         <v>31</v>
       </c>
       <c r="D40" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9633657932281494</v>
+        <v>0.9608070254325867</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3571358323097229</v>
+        <v>0.3064244091510773</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.9556941986083984</v>
+        <v>0.9528326392173767</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4617979824542999</v>
+        <v>0.4711657166481018</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1963,13 +1975,13 @@
         <v>31</v>
       </c>
       <c r="D41" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9565741419792175</v>
+        <v>0.9461261034011841</v>
       </c>
       <c r="F41" t="n">
-        <v>0.236223503947258</v>
+        <v>0.121971070766449</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.9092104434967041</v>
+        <v>0.897868275642395</v>
       </c>
       <c r="I41" t="n">
-        <v>0.06156635656952858</v>
+        <v>0.05275560170412064</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2001,13 +2013,13 @@
         <v>31</v>
       </c>
       <c r="D42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E42" t="n">
-        <v>0.95151287317276</v>
+        <v>0.9519780278205872</v>
       </c>
       <c r="F42" t="n">
-        <v>0.1718403846025467</v>
+        <v>0.1769774556159973</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9092130661010742</v>
+        <v>0.910927414894104</v>
       </c>
       <c r="I42" t="n">
-        <v>0.06157348677515984</v>
+        <v>0.08933524787425995</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2039,13 +2051,13 @@
         <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9777392148971558</v>
+        <v>0.9783721566200256</v>
       </c>
       <c r="F43" t="n">
-        <v>0.747298002243042</v>
+        <v>0.7660117149353027</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9558780193328857</v>
+        <v>0.9421800374984741</v>
       </c>
       <c r="I43" t="n">
-        <v>0.465127170085907</v>
+        <v>0.3156377673149109</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2077,13 +2089,13 @@
         <v>31</v>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9692672491073608</v>
+        <v>0.9754472374916077</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4991283416748047</v>
+        <v>0.6783064603805542</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9131918549537659</v>
+        <v>0.920246958732605</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0733368843793869</v>
+        <v>0.1305810064077377</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2115,13 +2127,13 @@
         <v>31</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9532986879348755</v>
+        <v>0.9534594416618347</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1923774927854538</v>
+        <v>0.1943372935056686</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9700977206230164</v>
+        <v>0.9648153781890869</v>
       </c>
       <c r="I45" t="n">
-        <v>0.7569372057914734</v>
+        <v>0.6964844465255737</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2153,13 +2165,13 @@
         <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9352495670318604</v>
+        <v>0.9440911412239075</v>
       </c>
       <c r="F46" t="n">
-        <v>0.06102762743830681</v>
+        <v>0.1071163713932037</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9301799535751343</v>
+        <v>0.9196019172668457</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1556531935930252</v>
+        <v>0.1271905899047852</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2191,13 +2203,13 @@
         <v>31</v>
       </c>
       <c r="D47" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9546459913253784</v>
+        <v>0.9509859681129456</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2093967795372009</v>
+        <v>0.1661946773529053</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9469863772392273</v>
+        <v>0.9530481100082397</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3236485719680786</v>
+        <v>0.4748136401176453</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2229,13 +2241,13 @@
         <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9647080898284912</v>
+        <v>0.9655840396881104</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3863736689090729</v>
+        <v>0.4064401984214783</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9760661721229553</v>
+        <v>0.9663005471229553</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8739327192306519</v>
+        <v>0.7259600162506104</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2267,24 +2279,24 @@
         <v>31</v>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9194356799125671</v>
+        <v>0.9339348673820496</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0228067971765995</v>
+        <v>0.05615990608930588</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8811495304107666</v>
+        <v>0.868415355682373</v>
       </c>
       <c r="I49" t="n">
-        <v>0.01855607330799103</v>
+        <v>0.01675647683441639</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2305,13 +2317,13 @@
         <v>31</v>
       </c>
       <c r="D50" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9739980697631836</v>
+        <v>0.9727019071578979</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6346335411071777</v>
+        <v>0.5961378216743469</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,10 +2331,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9141044616699219</v>
+        <v>0.9092689752578735</v>
       </c>
       <c r="I50" t="n">
-        <v>0.07634661346673965</v>
+        <v>0.08351875096559525</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2343,13 +2355,13 @@
         <v>31</v>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9868044257164001</v>
+        <v>0.9873507022857666</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9598984718322754</v>
+        <v>0.9669033885002136</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.9570492506027222</v>
+        <v>0.9468318223953247</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4867151975631714</v>
+        <v>0.3775015473365784</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2381,13 +2393,13 @@
         <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9732822179794312</v>
+        <v>0.9630803465843201</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6132808923721313</v>
+        <v>0.3511536121368408</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9129328727722168</v>
+        <v>0.9165458679199219</v>
       </c>
       <c r="I52" t="n">
-        <v>0.07250509411096573</v>
+        <v>0.1122886911034584</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2419,13 +2431,13 @@
         <v>31</v>
       </c>
       <c r="D53" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9386389851570129</v>
+        <v>0.935591459274292</v>
       </c>
       <c r="F53" t="n">
-        <v>0.07567121088504791</v>
+        <v>0.06236302107572556</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.933374285697937</v>
+        <v>0.9369404911994934</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1792816519737244</v>
+        <v>0.2566979229450226</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2457,13 +2469,13 @@
         <v>31</v>
       </c>
       <c r="D54" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9564789533615112</v>
+        <v>0.9472880959510803</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2348271906375885</v>
+        <v>0.1313543170690536</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.942176342010498</v>
+        <v>0.9551652669906616</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2635136842727661</v>
+        <v>0.5116387605667114</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2495,13 +2507,13 @@
         <v>31</v>
       </c>
       <c r="D55" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9402920603752136</v>
+        <v>0.9449414014816284</v>
       </c>
       <c r="F55" t="n">
-        <v>0.08406706899404526</v>
+        <v>0.1130896583199501</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9377760887145996</v>
+        <v>0.9394243955612183</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2175906598567963</v>
+        <v>0.2832807600498199</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2533,13 +2545,13 @@
         <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E56" t="n">
-        <v>0.907257080078125</v>
+        <v>0.9091507196426392</v>
       </c>
       <c r="F56" t="n">
-        <v>0.01099248416721821</v>
+        <v>0.01229176204651594</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9521690607070923</v>
+        <v>0.9287714958190918</v>
       </c>
       <c r="I56" t="n">
-        <v>0.40121990442276</v>
+        <v>0.1847572326660156</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2571,13 +2583,13 @@
         <v>31</v>
       </c>
       <c r="D57" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E57" t="n">
-        <v>0.948672890663147</v>
+        <v>0.9393500685691833</v>
       </c>
       <c r="F57" t="n">
-        <v>0.1434708386659622</v>
+        <v>0.07917311042547226</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9258439540863037</v>
+        <v>0.9422754049301147</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1284162402153015</v>
+        <v>0.3168141841888428</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2609,13 +2621,13 @@
         <v>31</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9685860872268677</v>
+        <v>0.9724588394165039</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4810150265693665</v>
+        <v>0.5890077948570251</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.8980177044868469</v>
+        <v>0.8608572483062744</v>
       </c>
       <c r="I58" t="n">
-        <v>0.03786245733499527</v>
+        <v>0.01262117642909288</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2647,13 +2659,13 @@
         <v>31</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9244606494903564</v>
+        <v>0.9266564249992371</v>
       </c>
       <c r="F59" t="n">
-        <v>0.03105461783707142</v>
+        <v>0.03558455780148506</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2661,10 +2673,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9408773183822632</v>
+        <v>0.9326837062835693</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2491005659103394</v>
+        <v>0.2164284735918045</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2685,13 +2697,13 @@
         <v>31</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E60" t="n">
-        <v>0.947057843208313</v>
+        <v>0.9499154090881348</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1294398307800293</v>
+        <v>0.1552724838256836</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9846987724304199</v>
+        <v>0.9766345620155334</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9796587824821472</v>
+        <v>0.9088447093963623</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2723,13 +2735,13 @@
         <v>31</v>
       </c>
       <c r="D61" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E61" t="n">
-        <v>0.947356641292572</v>
+        <v>0.9521634578704834</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1319295465946198</v>
+        <v>0.1790657192468643</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9531307816505432</v>
+        <v>0.9626709222793579</v>
       </c>
       <c r="I61" t="n">
-        <v>0.4171240925788879</v>
+        <v>0.6539081931114197</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2761,24 +2773,24 @@
         <v>31</v>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9363393187522888</v>
+        <v>0.9240401387214661</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06538931280374527</v>
+        <v>0.03025784716010094</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.9318616986274719</v>
+        <v>0.9410133361816406</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1676865220069885</v>
+        <v>0.3015600144863129</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2799,13 +2811,13 @@
         <v>31</v>
       </c>
       <c r="D63" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9748712778091431</v>
+        <v>0.9818515181541443</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6609015464782715</v>
+        <v>0.8619628548622131</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,10 +2825,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.915461540222168</v>
+        <v>0.9224836230278015</v>
       </c>
       <c r="I63" t="n">
-        <v>0.08105841279029846</v>
+        <v>0.1430508941411972</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2837,13 +2849,13 @@
         <v>31</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9695011973381042</v>
+        <v>0.9672315716743469</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5054442882537842</v>
+        <v>0.4462774693965912</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9297296404838562</v>
+        <v>0.9496259093284607</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1525775641202927</v>
+        <v>0.4191780388355255</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2875,13 +2887,13 @@
         <v>31</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E65" t="n">
-        <v>0.89936363697052</v>
+        <v>0.9082309603691101</v>
       </c>
       <c r="F65" t="n">
-        <v>0.006949448492377996</v>
+        <v>0.01164162252098322</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9454333186149597</v>
+        <v>0.9401009082794189</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3030279278755188</v>
+        <v>0.2909397184848785</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2913,13 +2925,13 @@
         <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9630050659179688</v>
+        <v>0.958779513835907</v>
       </c>
       <c r="F66" t="n">
-        <v>0.3495900630950928</v>
+        <v>0.2707603871822357</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9312317371368408</v>
+        <v>0.9501950740814209</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1630759835243225</v>
+        <v>0.4280851185321808</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2951,13 +2963,13 @@
         <v>31</v>
       </c>
       <c r="D67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E67" t="n">
-        <v>0.8998947143554688</v>
+        <v>0.9308784008026123</v>
       </c>
       <c r="F67" t="n">
-        <v>0.007164604496210814</v>
+        <v>0.04632744938135147</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,14 +2977,14 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.89158695936203</v>
+        <v>0.9068350195884705</v>
       </c>
       <c r="I67" t="n">
-        <v>0.02876358106732368</v>
+        <v>0.07567598670721054</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -2989,13 +3001,13 @@
         <v>31</v>
       </c>
       <c r="D68" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9559932351112366</v>
+        <v>0.9605070948600769</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2278229743242264</v>
+        <v>0.3009022772312164</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9460316300392151</v>
+        <v>0.9638480544090271</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3108320534229279</v>
+        <v>0.677252471446991</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3027,13 +3039,13 @@
         <v>31</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E69" t="n">
-        <v>0.8564706444740295</v>
+        <v>0.8681620955467224</v>
       </c>
       <c r="F69" t="n">
-        <v>0.0006980623584240675</v>
+        <v>0.001266348059289157</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8596469759941101</v>
+        <v>0.8737738728523254</v>
       </c>
       <c r="I69" t="n">
-        <v>0.007767383009195328</v>
+        <v>0.02054273523390293</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3065,13 +3077,13 @@
         <v>31</v>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9769468307495117</v>
+        <v>0.9730761647224426</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7235919237136841</v>
+        <v>0.6071747541427612</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.967048168182373</v>
+        <v>0.9733871221542358</v>
       </c>
       <c r="I70" t="n">
-        <v>0.691734254360199</v>
+        <v>0.8584069609642029</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3103,13 +3115,13 @@
         <v>31</v>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9528040289878845</v>
+        <v>0.9521031379699707</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1864648312330246</v>
+        <v>0.178383857011795</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.8883594870567322</v>
+        <v>0.8555963635444641</v>
       </c>
       <c r="I71" t="n">
-        <v>0.02509131655097008</v>
+        <v>0.01039002276957035</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3141,13 +3153,13 @@
         <v>31</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9185682535171509</v>
+        <v>0.9143255352973938</v>
       </c>
       <c r="F72" t="n">
-        <v>0.02163257077336311</v>
+        <v>0.016736114397645</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.9686148762702942</v>
+        <v>0.9304932951927185</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7253944873809814</v>
+        <v>0.1981060355901718</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3179,24 +3191,24 @@
         <v>31</v>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9331586360931396</v>
+        <v>0.9294945597648621</v>
       </c>
       <c r="F73" t="n">
-        <v>0.05347500368952751</v>
+        <v>0.04247784614562988</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9867196083068848</v>
+        <v>0.9861395955085754</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9901552200317383</v>
+        <v>0.9913190603256226</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3217,13 +3229,13 @@
         <v>31</v>
       </c>
       <c r="D74" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9094729423522949</v>
+        <v>0.9222176074981689</v>
       </c>
       <c r="F74" t="n">
-        <v>0.01252847630530596</v>
+        <v>0.02704324945807457</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9632279872894287</v>
+        <v>0.9641457200050354</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6101504564285278</v>
+        <v>0.6831690073013306</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3255,13 +3267,13 @@
         <v>31</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9532285332679749</v>
+        <v>0.9537062644958496</v>
       </c>
       <c r="F75" t="n">
-        <v>0.1915284842252731</v>
+        <v>0.1973828375339508</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3269,10 +3281,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.9279093742370605</v>
+        <v>0.9280836582183838</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1407443881034851</v>
+        <v>0.179670661687851</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3293,13 +3305,13 @@
         <v>31</v>
       </c>
       <c r="D76" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9666802287101746</v>
+        <v>0.966705322265625</v>
       </c>
       <c r="F76" t="n">
-        <v>0.4326458275318146</v>
+        <v>0.4332593679428101</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9359952807426453</v>
+        <v>0.9573099613189697</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2012333124876022</v>
+        <v>0.5506460070610046</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3331,13 +3343,13 @@
         <v>31</v>
       </c>
       <c r="D77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9740888476371765</v>
+        <v>0.9799010753631592</v>
       </c>
       <c r="F77" t="n">
-        <v>0.6373555064201355</v>
+        <v>0.8099411129951477</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9239292144775391</v>
+        <v>0.9324101805686951</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1179520934820175</v>
+        <v>0.214055210351944</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3369,13 +3381,13 @@
         <v>31</v>
       </c>
       <c r="D78" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9118698239326477</v>
+        <v>0.9174463748931885</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01444718800485134</v>
+        <v>0.0202071126550436</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9705832600593567</v>
+        <v>0.958051323890686</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7671448588371277</v>
+        <v>0.5644877552986145</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3407,13 +3419,13 @@
         <v>31</v>
       </c>
       <c r="D79" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9610446095466614</v>
+        <v>0.9628718495368958</v>
       </c>
       <c r="F79" t="n">
-        <v>0.3108602166175842</v>
+        <v>0.3468362092971802</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3421,10 +3433,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.8090236186981201</v>
+        <v>0.7784209251403809</v>
       </c>
       <c r="I79" t="n">
-        <v>0.001181461848318577</v>
+        <v>0.000764878059271723</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3445,13 +3457,13 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9005547761917114</v>
+        <v>0.8930658102035522</v>
       </c>
       <c r="F80" t="n">
-        <v>0.007441859226673841</v>
+        <v>0.004860051441937685</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9245864152908325</v>
+        <v>0.9064919352531433</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1214440017938614</v>
+        <v>0.07463277131319046</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3483,24 +3495,24 @@
         <v>31</v>
       </c>
       <c r="D81" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9211173057556152</v>
+        <v>0.9331881999969482</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0252770371735096</v>
+        <v>0.0535748265683651</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.8838134407997131</v>
+        <v>0.8944951891899109</v>
       </c>
       <c r="I81" t="n">
-        <v>0.02073285356163979</v>
+        <v>0.04611574113368988</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3521,24 +3533,24 @@
         <v>31</v>
       </c>
       <c r="D82" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9318587183952332</v>
+        <v>0.9441038370132446</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0492711216211319</v>
+        <v>0.1072031483054161</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.7656641006469727</v>
+        <v>0.7815759778022766</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0002774915192276239</v>
+        <v>0.0008439520606771111</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3559,13 +3571,13 @@
         <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9090703725814819</v>
+        <v>0.9097738862037659</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01223351806402206</v>
+        <v>0.01275391224771738</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.928322970867157</v>
+        <v>0.9030848145484924</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1433506906032562</v>
+        <v>0.06504283845424652</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3597,28 +3609,28 @@
         <v>31</v>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9268341660499573</v>
+        <v>0.9421125650405884</v>
       </c>
       <c r="F84" t="n">
-        <v>0.03598015755414963</v>
+        <v>0.09441179037094116</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.894530713558197</v>
+        <v>0.8996981978416443</v>
       </c>
       <c r="I84" t="n">
-        <v>0.03260578587651253</v>
+        <v>0.05676604062318802</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3635,13 +3647,13 @@
         <v>31</v>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9622119069099426</v>
+        <v>0.9456152319908142</v>
       </c>
       <c r="F85" t="n">
-        <v>0.3334590196609497</v>
+        <v>0.1180591061711311</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,14 +3661,14 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.8851776123046875</v>
+        <v>0.9030956625938416</v>
       </c>
       <c r="I85" t="n">
-        <v>0.02195023372769356</v>
+        <v>0.06507116556167603</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3685,13 @@
         <v>31</v>
       </c>
       <c r="D86" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E86" t="n">
-        <v>0.8878344297409058</v>
+        <v>0.9098964333534241</v>
       </c>
       <c r="F86" t="n">
-        <v>0.003630924737080932</v>
+        <v>0.01284696348011494</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3687,10 +3699,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.9152907133102417</v>
+        <v>0.9080763459205627</v>
       </c>
       <c r="I86" t="n">
-        <v>0.08044920861721039</v>
+        <v>0.07957672327756882</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3711,13 +3723,13 @@
         <v>31</v>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9718073010444641</v>
+        <v>0.9648562073707581</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5700688362121582</v>
+        <v>0.3897110521793365</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9770780205726624</v>
+        <v>0.9716562628746033</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8910690546035767</v>
+        <v>0.828197717666626</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3749,13 +3761,13 @@
         <v>31</v>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9784141778945923</v>
+        <v>0.9767041206359863</v>
       </c>
       <c r="F88" t="n">
-        <v>0.7672452330589294</v>
+        <v>0.7162855863571167</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.8877078890800476</v>
+        <v>0.8760450482368469</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02441157400608063</v>
+        <v>0.02241085469722748</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3787,13 +3799,13 @@
         <v>31</v>
       </c>
       <c r="D89" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9745556116104126</v>
+        <v>0.9703915119171143</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6513853669166565</v>
+        <v>0.529904305934906</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,10 +3813,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.8613507151603699</v>
+        <v>0.8690972924232483</v>
       </c>
       <c r="I89" t="n">
-        <v>0.008309000171720982</v>
+        <v>0.01719437912106514</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -3825,13 +3837,13 @@
         <v>31</v>
       </c>
       <c r="D90" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E90" t="n">
-        <v>0.938984751701355</v>
+        <v>0.9471771121025085</v>
       </c>
       <c r="F90" t="n">
-        <v>0.07735381275415421</v>
+        <v>0.1304277181625366</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.8633113503456116</v>
+        <v>0.8533579707145691</v>
       </c>
       <c r="I90" t="n">
-        <v>0.008982216008007526</v>
+        <v>0.009571204893290997</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3863,13 +3875,13 @@
         <v>31</v>
       </c>
       <c r="D91" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9399312734603882</v>
+        <v>0.9355555772781372</v>
       </c>
       <c r="F91" t="n">
-        <v>0.08215752243995667</v>
+        <v>0.0622214749455452</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.9706971645355225</v>
+        <v>0.9578890800476074</v>
       </c>
       <c r="I91" t="n">
-        <v>0.769528329372406</v>
+        <v>0.5614445209503174</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3901,13 +3913,13 @@
         <v>31</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9394095540046692</v>
+        <v>0.9359567165374756</v>
       </c>
       <c r="F92" t="n">
-        <v>0.07947344332933426</v>
+        <v>0.06382272392511368</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,14 +3927,14 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.9036148190498352</v>
+        <v>0.923875093460083</v>
       </c>
       <c r="I92" t="n">
-        <v>0.04822738468647003</v>
+        <v>0.1513980180025101</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3939,13 +3951,13 @@
         <v>31</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9583844542503357</v>
+        <v>0.9702089428901672</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2642559409141541</v>
+        <v>0.5248351693153381</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,10 +3965,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.9395354986190796</v>
+        <v>0.9444139003753662</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2349777370691299</v>
+        <v>0.3441855907440186</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -3977,13 +3989,13 @@
         <v>31</v>
       </c>
       <c r="D94" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9487008452415466</v>
+        <v>0.9483936429023743</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1437267512083054</v>
+        <v>0.1409422755241394</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.9440531730651855</v>
+        <v>0.9536610841751099</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2856793105602264</v>
+        <v>0.4852930009365082</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4015,13 +4027,13 @@
         <v>31</v>
       </c>
       <c r="D95" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9686346054077148</v>
+        <v>0.9736404418945312</v>
       </c>
       <c r="F95" t="n">
-        <v>0.482290506362915</v>
+        <v>0.6239420175552368</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9570868611335754</v>
+        <v>0.9475558400154114</v>
       </c>
       <c r="I95" t="n">
-        <v>0.4874196648597717</v>
+        <v>0.3879734575748444</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4053,13 +4065,13 @@
         <v>31</v>
       </c>
       <c r="D96" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E96" t="n">
-        <v>0.9006472826004028</v>
+        <v>0.9165316224098206</v>
       </c>
       <c r="F96" t="n">
-        <v>0.007481604348868132</v>
+        <v>0.01911766082048416</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4067,14 +4079,14 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.9013628363609314</v>
+        <v>0.911567211151123</v>
       </c>
       <c r="I96" t="n">
-        <v>0.04374075680971146</v>
+        <v>0.09168821573257446</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4091,28 +4103,28 @@
         <v>31</v>
       </c>
       <c r="D97" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E97" t="n">
-        <v>0.920160710811615</v>
+        <v>0.9336433410644531</v>
       </c>
       <c r="F97" t="n">
-        <v>0.02383936941623688</v>
+        <v>0.05513564497232437</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.893274188041687</v>
+        <v>0.9495618343353271</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03090391308069229</v>
+        <v>0.4181848466396332</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4129,13 +4141,13 @@
         <v>31</v>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9572276473045349</v>
+        <v>0.9565014243125916</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2460141479969025</v>
+        <v>0.2351562827825546</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,10 +4155,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.8898921608924866</v>
+        <v>0.8630038499832153</v>
       </c>
       <c r="I98" t="n">
-        <v>0.02676963806152344</v>
+        <v>0.0136726526543498</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4167,13 +4179,13 @@
         <v>31</v>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8826652765274048</v>
+        <v>0.8940137028694153</v>
       </c>
       <c r="F99" t="n">
-        <v>0.002735225716605783</v>
+        <v>0.005126417148858309</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.9599480032920837</v>
+        <v>0.9472535252571106</v>
       </c>
       <c r="I99" t="n">
-        <v>0.5428107976913452</v>
+        <v>0.3835729956626892</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4205,13 +4217,13 @@
         <v>31</v>
       </c>
       <c r="D100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9384015798568726</v>
+        <v>0.9472572207450867</v>
       </c>
       <c r="F100" t="n">
-        <v>0.07453735917806625</v>
+        <v>0.1310956627130508</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.9515828490257263</v>
+        <v>0.9506001472473145</v>
       </c>
       <c r="I100" t="n">
-        <v>0.3917574286460876</v>
+        <v>0.4345090985298157</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4243,28 +4255,28 @@
         <v>31</v>
       </c>
       <c r="D101" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9415789842605591</v>
+        <v>0.9310870766639709</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0912531390786171</v>
+        <v>0.04693835973739624</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.8910501599311829</v>
+        <v>0.9109823703765869</v>
       </c>
       <c r="I101" t="n">
-        <v>0.02811568416655064</v>
+        <v>0.08953502029180527</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4281,13 +4293,13 @@
         <v>31</v>
       </c>
       <c r="D102" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E102" t="n">
-        <v>0.960276186466217</v>
+        <v>0.9592509865760803</v>
       </c>
       <c r="F102" t="n">
-        <v>0.296709805727005</v>
+        <v>0.2787087559700012</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.9630539417266846</v>
+        <v>0.9562767744064331</v>
       </c>
       <c r="I102" t="n">
-        <v>0.6064935922622681</v>
+        <v>0.5316527485847473</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4319,13 +4331,13 @@
         <v>31</v>
       </c>
       <c r="D103" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9372979998588562</v>
+        <v>0.9478159546852112</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0694902241230011</v>
+        <v>0.1358493566513062</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.9690960645675659</v>
+        <v>0.969916045665741</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7356792092323303</v>
+        <v>0.7961087226867676</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4357,13 +4369,13 @@
         <v>31</v>
       </c>
       <c r="D104" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9810321927070618</v>
+        <v>0.9828750491142273</v>
       </c>
       <c r="F104" t="n">
-        <v>0.8407852053642273</v>
+        <v>0.8867563009262085</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -4371,10 +4383,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.8587420582771301</v>
+        <v>0.8612512350082397</v>
       </c>
       <c r="I104" t="n">
-        <v>0.007495060097426176</v>
+        <v>0.01280754897743464</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4395,13 +4407,13 @@
         <v>31</v>
       </c>
       <c r="D105" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8987916707992554</v>
+        <v>0.8856391906738281</v>
       </c>
       <c r="F105" t="n">
-        <v>0.00672532944008708</v>
+        <v>0.003217509249225259</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4409,14 +4421,14 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.92743980884552</v>
+        <v>0.8942352533340454</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1378419995307922</v>
+        <v>0.04564161598682404</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4433,13 +4445,13 @@
         <v>31</v>
       </c>
       <c r="D106" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9524083733558655</v>
+        <v>0.9664229154586792</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1818609535694122</v>
+        <v>0.4263853430747986</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -4447,10 +4459,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.9546349048614502</v>
+        <v>0.9325626492500305</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4429400265216827</v>
+        <v>0.2153749614953995</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4471,13 +4483,13 @@
         <v>31</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9508816003799438</v>
+        <v>0.9521666169166565</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1650977432727814</v>
+        <v>0.1791021525859833</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,10 +4497,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.9784904718399048</v>
+        <v>0.9858539700508118</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9131497740745544</v>
+        <v>0.9903095960617065</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4509,13 +4521,13 @@
         <v>31</v>
       </c>
       <c r="D108" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8781670928001404</v>
+        <v>0.8672422170639038</v>
       </c>
       <c r="F108" t="n">
-        <v>0.002145846141502261</v>
+        <v>0.001207418390549719</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.9299457669258118</v>
+        <v>0.9231674075126648</v>
       </c>
       <c r="I108" t="n">
-        <v>0.1540461629629135</v>
+        <v>0.147094264626503</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4547,13 +4559,13 @@
         <v>31</v>
       </c>
       <c r="D109" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9229262471199036</v>
+        <v>0.9192951321601868</v>
       </c>
       <c r="F109" t="n">
-        <v>0.02824862860143185</v>
+        <v>0.02261208184063435</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.8525662422180176</v>
+        <v>0.816744327545166</v>
       </c>
       <c r="I109" t="n">
-        <v>0.005886830855160952</v>
+        <v>0.002644539810717106</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4585,13 +4597,13 @@
         <v>31</v>
       </c>
       <c r="D110" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9593700170516968</v>
+        <v>0.9499441385269165</v>
       </c>
       <c r="F110" t="n">
-        <v>0.2807483077049255</v>
+        <v>0.1555563360452652</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9582911729812622</v>
+        <v>0.9445469975471497</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5103018879890442</v>
+        <v>0.3459534645080566</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4623,13 +4635,13 @@
         <v>31</v>
       </c>
       <c r="D111" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8998375535011292</v>
+        <v>0.8813909888267517</v>
       </c>
       <c r="F111" t="n">
-        <v>0.007141107227653265</v>
+        <v>0.002552589867264032</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,10 +4649,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.968139111995697</v>
+        <v>0.9688594937324524</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7151942849159241</v>
+        <v>0.775986909866333</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4661,13 +4673,13 @@
         <v>31</v>
       </c>
       <c r="D112" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9547576904296875</v>
+        <v>0.9615105390548706</v>
       </c>
       <c r="F112" t="n">
-        <v>0.2108701020479202</v>
+        <v>0.3197188675403595</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.8519147038459778</v>
+        <v>0.860360324382782</v>
       </c>
       <c r="I112" t="n">
-        <v>0.005739916115999222</v>
+        <v>0.01239018607884645</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4699,13 +4711,13 @@
         <v>31</v>
       </c>
       <c r="D113" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9657405614852905</v>
+        <v>0.9714944958686829</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4101085364818573</v>
+        <v>0.5610710978507996</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,14 +4725,14 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9126186966896057</v>
+        <v>0.8837089538574219</v>
       </c>
       <c r="I113" t="n">
-        <v>0.07150895893573761</v>
+        <v>0.03015115298330784</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4737,13 +4749,13 @@
         <v>31</v>
       </c>
       <c r="D114" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9795403480529785</v>
+        <v>0.9508976936340332</v>
       </c>
       <c r="F114" t="n">
-        <v>0.7997772097587585</v>
+        <v>0.1652662307024002</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,14 +4763,14 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.9059146642684937</v>
+        <v>0.8565710783004761</v>
       </c>
       <c r="I114" t="n">
-        <v>0.05330510064959526</v>
+        <v>0.01076951250433922</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4775,13 +4787,13 @@
         <v>31</v>
       </c>
       <c r="D115" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9759357571601868</v>
+        <v>0.97739177942276</v>
       </c>
       <c r="F115" t="n">
-        <v>0.6930822730064392</v>
+        <v>0.736935555934906</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9428530335426331</v>
+        <v>0.955128014087677</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2713197469711304</v>
+        <v>0.51097571849823</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4813,13 +4825,13 @@
         <v>31</v>
       </c>
       <c r="D116" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E116" t="n">
-        <v>0.9187473058700562</v>
+        <v>0.8936138153076172</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02186973765492439</v>
+        <v>0.005012200679630041</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4827,10 +4839,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.9268865585327148</v>
+        <v>0.9286175966262817</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1344986259937286</v>
+        <v>0.1836069375276566</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4851,13 +4863,13 @@
         <v>31</v>
       </c>
       <c r="D117" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9498778581619263</v>
+        <v>0.9462825655937195</v>
       </c>
       <c r="F117" t="n">
-        <v>0.1549020409584045</v>
+        <v>0.1231943145394325</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.8481339812278748</v>
+        <v>0.8240887522697449</v>
       </c>
       <c r="I117" t="n">
-        <v>0.004960802383720875</v>
+        <v>0.0033946274779737</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4889,24 +4901,24 @@
         <v>31</v>
       </c>
       <c r="D118" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9391971230506897</v>
+        <v>0.9301901459693909</v>
       </c>
       <c r="F118" t="n">
-        <v>0.07840612530708313</v>
+        <v>0.04436959326267242</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9093509316444397</v>
+        <v>0.912377655506134</v>
       </c>
       <c r="I118" t="n">
-        <v>0.06194666773080826</v>
+        <v>0.09475959837436676</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4927,13 +4939,13 @@
         <v>31</v>
       </c>
       <c r="D119" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9590391516685486</v>
+        <v>0.9584214687347412</v>
       </c>
       <c r="F119" t="n">
-        <v>0.2751122117042542</v>
+        <v>0.2648596167564392</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9723515510559082</v>
+        <v>0.976518452167511</v>
       </c>
       <c r="I119" t="n">
-        <v>0.8035624623298645</v>
+        <v>0.9072076678276062</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4965,13 +4977,13 @@
         <v>31</v>
       </c>
       <c r="D120" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8923219442367554</v>
+        <v>0.8991121649742126</v>
       </c>
       <c r="F120" t="n">
-        <v>0.004661257378757</v>
+        <v>0.006849957630038261</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9194201827049255</v>
+        <v>0.9256795048713684</v>
       </c>
       <c r="I120" t="n">
-        <v>0.09657160192728043</v>
+        <v>0.1629416644573212</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5003,13 +5015,13 @@
         <v>31</v>
       </c>
       <c r="D121" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9780381917953491</v>
+        <v>0.9877634048461914</v>
       </c>
       <c r="F121" t="n">
-        <v>0.7561671733856201</v>
+        <v>0.9716646671295166</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.9330715537071228</v>
+        <v>0.9256449937820435</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1769004017114639</v>
+        <v>0.162712886929512</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
